--- a/docs/compliance/spreadsheets/CAIQ.xlsx
+++ b/docs/compliance/spreadsheets/CAIQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAIQ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CAIQ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CAIQ'!$A$1:$F$73</definedName>
@@ -566,7 +566,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Last reviewed: 2026-08-25</t>
+          <t>Last reviewed: 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Enforced by the database: RLS ENABLE and FORCE on 82 of 88 tables, 197 policies, and a database per customer.</t>
+          <t>Enforced by the database: RLS ENABLE and FORCE on 83 of 89 tables, 205 policies, and a database per customer.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Roles and permissions are seed rows; 35 enforced keys, granted per branch.</t>
+          <t>Roles and permissions are seed rows; 38 enforced keys, granted and checked per branch.</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>TOTP, and mandatory for Administrator and Finance — enforced in both internal shells.</t>
+          <t>TOTP, and mandatory for Administrator and Finance — enforced in both internal shells. Backup codes accepted at the challenge.</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Five failures locks the account for fifteen minutes; ten attempts per address per fifteen minutes.</t>
+          <t>Five failures locks the account for fifteen minutes; ten attempts per address per fifteen minutes. Enforced inside Better Auth; the address comes from the trusted proxy hops, never the leftmost X-Forwarded-For entry.</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Database-backed and opaque, never JWTs. Revocation takes effect on the next request. 12-hour expiry, __Secure- cookies.</t>
+          <t>Database-backed and opaque, never JWTs. Revocation takes effect on the next request; sign-out deletes the session and a reset revokes all of them. 12-hour expiry, __Secure- cookies.</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>80 audit triggers; vendor support access separately granted, time-boxed, read-only by structure, logged per transaction.</t>
+          <t>81 audit triggers; vendor support access separately granted, time-boxed, read-only unless the customer grants write scope, logged per transaction.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">

--- a/docs/compliance/spreadsheets/CAIQ.xlsx
+++ b/docs/compliance/spreadsheets/CAIQ.xlsx
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Enforced by the database: RLS ENABLE and FORCE on 83 of 89 tables, 205 policies, and a database per customer.</t>
+          <t>Enforced by the database: RLS ENABLE and FORCE on 87 of 93 tables, 211 policies, and a database per customer.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>81 audit triggers; vendor support access separately granted, time-boxed, read-only unless the customer grants write scope, logged per transaction.</t>
+          <t>85 audit triggers; vendor support access separately granted, time-boxed, read-only unless the customer grants write scope, logged per transaction.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
